--- a/Dataset/EN/xlsx/ITAMed_2025_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2025_EN.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pediatrics</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Oncology</t>
+          <t>Gastroenterology; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>General Surgery; Gastroenterology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>General Surgery; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pediatrics</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pediatrics</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Urology; Pharmacology and Toxicology</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Urology; Medical Genetics</t>
+          <t>Urology; Oncology</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Gynecology and Obstetrics</t>
+          <t>Anesthesia and Intensive Care; Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Infectious Diseases</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Infectious Diseases</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Anesthesia and Intensive Care</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Orthopedics and Traumatology</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Hematology; Pharmacology and Toxicology</t>
+          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Medical Genetics; Immunology and Rheumatology</t>
+          <t>Medical Genetics</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Anesthesia and Intensive Care</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Endocrinology; Pharmacology and Toxicology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Occupational Medicine; Otorhinolaryngology</t>
+          <t>Occupational Medicine</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Gastroenterology; Hematology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Oncology</t>
+          <t>Gastroenterology; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Gastroenterology</t>
+          <t>Gastroenterology; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Oncology</t>
+          <t>Oncology; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Oncology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2025_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2025_EN.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8375,7 +8375,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/EN/xlsx/ITAMed_2025_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2025_EN.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -473,15 +473,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Question Type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Image Category</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Image Path</t>
         </is>
@@ -544,6 +549,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -602,6 +612,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -660,6 +675,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -718,6 +738,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -776,6 +801,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -834,6 +864,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -892,6 +927,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -950,6 +990,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1008,6 +1053,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1066,6 +1116,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1124,6 +1179,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1182,6 +1242,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1240,6 +1305,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1298,6 +1368,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1356,6 +1431,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1414,6 +1494,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1472,6 +1557,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1530,6 +1620,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1588,6 +1683,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1646,6 +1746,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1704,6 +1809,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1762,6 +1872,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1820,6 +1935,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1878,6 +1998,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1938,10 +2063,15 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>Brain CT scan</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>images/2025/ssm2025885.png</t>
         </is>
@@ -2004,6 +2134,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2062,6 +2197,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2120,6 +2260,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2178,6 +2323,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2236,6 +2386,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2294,6 +2449,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2352,6 +2512,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2412,10 +2577,15 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>Upper limb X-ray</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>images/2025/ssm2025893.png</t>
         </is>
@@ -2478,6 +2648,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2538,10 +2713,15 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>Audiometry report</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>images/2025/ssm2025895.png</t>
         </is>
@@ -2606,10 +2786,15 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>Otoscopic image</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>images/2025/ssm2025896.png</t>
         </is>
@@ -2672,6 +2857,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2730,6 +2920,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2788,6 +2983,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2846,6 +3046,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2904,6 +3109,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2964,10 +3174,15 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>images/2025/ssm2025902.png</t>
         </is>
@@ -3032,10 +3247,15 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>images/2025/ssm2025903.png</t>
         </is>
@@ -3098,6 +3318,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3156,6 +3381,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3214,6 +3444,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3272,6 +3507,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3330,6 +3570,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3388,6 +3633,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3446,6 +3696,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3504,6 +3759,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3562,6 +3822,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3622,10 +3887,15 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>images/2025/ssm2025913.png</t>
         </is>
@@ -3690,10 +3960,15 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>images/2025/ssm2025914.png</t>
         </is>
@@ -3756,6 +4031,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3814,6 +4094,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3872,6 +4157,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3930,6 +4220,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3988,6 +4283,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4048,10 +4348,15 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
           <t>Chest X-ray</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>images/2025/ssm2025920.png</t>
         </is>
@@ -4114,6 +4419,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4172,6 +4482,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4230,6 +4545,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4290,10 +4610,15 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
           <t>Endoscopic image</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>images/2025/ssm2025924.png</t>
         </is>
@@ -4356,6 +4681,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4414,6 +4744,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4472,6 +4807,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4530,6 +4870,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4588,6 +4933,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4646,6 +4996,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4706,10 +5061,15 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
           <t>Chest X-ray</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>images/2025/ssm2025931.png</t>
         </is>
@@ -4769,7 +5129,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4830,6 +5195,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4888,6 +5258,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4946,6 +5321,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5004,6 +5384,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5062,6 +5447,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5120,6 +5510,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5178,6 +5573,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5236,6 +5636,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5294,6 +5699,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5352,6 +5762,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5410,6 +5825,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5468,6 +5888,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5526,6 +5951,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5584,6 +6014,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5642,6 +6077,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5700,6 +6140,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5758,6 +6203,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5816,6 +6266,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5874,6 +6329,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5932,6 +6392,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5990,6 +6455,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6048,6 +6518,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6106,6 +6581,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6164,6 +6644,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6224,10 +6709,15 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
           <t>Chest X-ray</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
+      <c r="O98" t="inlineStr">
         <is>
           <t>images/2025/ssm2025957.png</t>
         </is>
@@ -6290,6 +6780,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6348,6 +6843,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6406,6 +6906,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6464,6 +6969,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6522,6 +7032,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6580,6 +7095,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6638,6 +7158,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6696,6 +7221,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6754,6 +7284,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6812,6 +7347,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6870,6 +7410,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6928,6 +7473,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6986,6 +7536,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7044,6 +7599,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7102,6 +7662,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7160,6 +7725,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7218,6 +7788,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7276,6 +7851,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7334,6 +7914,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7392,6 +7977,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7450,6 +8040,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7508,6 +8103,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7566,6 +8166,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7624,6 +8229,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7682,6 +8292,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7740,6 +8355,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7798,6 +8418,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7856,6 +8481,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7914,6 +8544,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7972,6 +8607,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8030,6 +8670,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8088,6 +8733,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8146,6 +8796,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8204,6 +8859,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8262,6 +8922,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8320,6 +8985,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8378,6 +9048,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8436,6 +9111,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8496,10 +9176,15 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
           <t>Upper limb X-ray</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr">
+      <c r="O137" t="inlineStr">
         <is>
           <t>images/2025/ssm2025996.png</t>
         </is>
@@ -8562,6 +9247,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8620,6 +9310,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8678,6 +9373,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8734,6 +9434,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
